--- a/esyluban/examples/release/DataTables/bonus/掉落表.xlsx
+++ b/esyluban/examples/release/DataTables/bonus/掉落表.xlsx
@@ -1462,7 +1462,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="E1:CD1"/>
+    <mergeCell ref="E2:CD2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
